--- a/research/traditional_assets/database/data/romania/romania_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1189</v>
+        <v>0.035</v>
       </c>
       <c r="E2">
-        <v>0.1415</v>
+        <v>0.04915</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.001008878224757188</v>
+        <v>0.0008561360388933237</v>
       </c>
       <c r="J2">
-        <v>0.00072782075874255</v>
+        <v>0.000738710040502977</v>
       </c>
       <c r="K2">
-        <v>734.718</v>
+        <v>668.89</v>
       </c>
       <c r="L2">
-        <v>0.3961171015742937</v>
+        <v>0.387245990852776</v>
       </c>
       <c r="M2">
-        <v>166.3</v>
+        <v>791.5999999999999</v>
       </c>
       <c r="N2">
-        <v>0.02518094545895036</v>
+        <v>0.1567555793184023</v>
       </c>
       <c r="O2">
-        <v>0.2263453461055806</v>
+        <v>1.183453183632585</v>
       </c>
       <c r="P2">
-        <v>151.9</v>
+        <v>769</v>
       </c>
       <c r="Q2">
-        <v>0.02300051482389994</v>
+        <v>0.1522802431731322</v>
       </c>
       <c r="R2">
-        <v>0.2067459896177853</v>
+        <v>1.149665864342418</v>
       </c>
       <c r="S2">
-        <v>14.40000000000001</v>
+        <v>22.60000000000002</v>
       </c>
       <c r="T2">
-        <v>0.08659049909801568</v>
+        <v>0.02854977261243055</v>
       </c>
       <c r="U2">
-        <v>3703.2</v>
+        <v>3481.2</v>
       </c>
       <c r="V2">
-        <v>0.5607340783138004</v>
+        <v>0.6893601853502049</v>
       </c>
       <c r="W2">
-        <v>0.1204238052299369</v>
+        <v>0.1201798374546083</v>
       </c>
       <c r="X2">
-        <v>0.06003243198678791</v>
+        <v>0.1101649918968362</v>
       </c>
       <c r="Y2">
-        <v>0.06039137324314897</v>
+        <v>0.01001484555777214</v>
       </c>
       <c r="Z2">
-        <v>0.6032196219625986</v>
+        <v>0.6141607234415678</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05470966114584214</v>
+        <v>0.08914274469279126</v>
       </c>
       <c r="AC2">
-        <v>-0.05434779184834464</v>
+        <v>-0.08914274469279126</v>
       </c>
       <c r="AD2">
-        <v>1689.7</v>
+        <v>4094.5</v>
       </c>
       <c r="AE2">
-        <v>4.543663343601835</v>
+        <v>3.005981100097809</v>
       </c>
       <c r="AF2">
-        <v>1694.243663343602</v>
+        <v>4097.505981100097</v>
       </c>
       <c r="AG2">
-        <v>-2008.956336656398</v>
+        <v>616.3059811000976</v>
       </c>
       <c r="AH2">
-        <v>0.2041640254578723</v>
+        <v>0.4479418525389772</v>
       </c>
       <c r="AI2">
-        <v>0.2548024631258052</v>
+        <v>0.5451561587592857</v>
       </c>
       <c r="AJ2">
-        <v>-0.4371816782387198</v>
+        <v>0.1087687216376912</v>
       </c>
       <c r="AK2">
-        <v>-0.6819166876760885</v>
+        <v>0.1527397936922187</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>607.8057553956835</v>
+        <v>1968.509615384615</v>
       </c>
       <c r="AP2">
-        <v>-722.6461642648916</v>
+        <v>296.30095245197</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0668</v>
+        <v>0.035</v>
       </c>
       <c r="E3">
-        <v>0.101</v>
+        <v>0.0295</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,34 +728,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.002612042617643262</v>
+        <v>0.002185962719852828</v>
       </c>
       <c r="J3">
-        <v>0.002079859298456069</v>
+        <v>0.001800734220531897</v>
       </c>
       <c r="K3">
-        <v>267.1</v>
+        <v>278</v>
       </c>
       <c r="L3">
-        <v>0.3728364042434394</v>
+        <v>0.4109386548410939</v>
       </c>
       <c r="M3">
-        <v>12.2</v>
+        <v>512.3</v>
       </c>
       <c r="N3">
-        <v>0.004322562358276644</v>
+        <v>0.2617916091777812</v>
       </c>
       <c r="O3">
-        <v>0.04567577686259827</v>
+        <v>1.842805755395683</v>
       </c>
       <c r="P3">
-        <v>12.2</v>
+        <v>512.3</v>
       </c>
       <c r="Q3">
-        <v>0.004322562358276644</v>
+        <v>0.2617916091777812</v>
       </c>
       <c r="R3">
-        <v>0.04567577686259827</v>
+        <v>1.842805755395683</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2038.9</v>
+        <v>1940.8</v>
       </c>
       <c r="V3">
-        <v>0.7223993764172336</v>
+        <v>0.9917727017221114</v>
       </c>
       <c r="W3">
-        <v>0.1204238052299369</v>
+        <v>0.1201798374546083</v>
       </c>
       <c r="X3">
-        <v>0.06003243198678791</v>
+        <v>0.1101117834063283</v>
       </c>
       <c r="Y3">
-        <v>0.06039137324314897</v>
+        <v>0.01006805404828003</v>
       </c>
       <c r="Z3">
-        <v>0.3213501856082309</v>
+        <v>0.652484661867212</v>
       </c>
       <c r="AA3">
-        <v>0.0006683631715978626</v>
+        <v>0.001174951458996472</v>
       </c>
       <c r="AB3">
-        <v>0.05470966114584214</v>
+        <v>0.08913504235639216</v>
       </c>
       <c r="AC3">
-        <v>-0.05404129797424428</v>
+        <v>-0.08796009089739569</v>
       </c>
       <c r="AD3">
-        <v>771.2</v>
+        <v>1527.9</v>
       </c>
       <c r="AE3">
-        <v>4.543663343601835</v>
+        <v>3.005981100097809</v>
       </c>
       <c r="AF3">
-        <v>775.7436633436018</v>
+        <v>1530.905981100098</v>
       </c>
       <c r="AG3">
-        <v>-1263.156336656398</v>
+        <v>-409.894018899902</v>
       </c>
       <c r="AH3">
-        <v>0.2155955225597458</v>
+        <v>0.4389309466741699</v>
       </c>
       <c r="AI3">
-        <v>0.2500266700003868</v>
+        <v>0.5506646118916348</v>
       </c>
       <c r="AJ3">
-        <v>-0.8101083662239925</v>
+        <v>-0.2649595566582235</v>
       </c>
       <c r="AK3">
-        <v>-1.187463089261556</v>
+        <v>-0.4883725698733188</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>277.4100719424461</v>
+        <v>734.5673076923077</v>
       </c>
       <c r="AP3">
-        <v>-454.3727829699275</v>
+        <v>-197.0644321634144</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banca Transilvania S.A. (BVB:TLV)</t>
+          <t>Patria Bank SA (BVB:PBK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +844,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.171</v>
-      </c>
-      <c r="E4">
-        <v>0.182</v>
+        <v>-0.0004</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,85 +859,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>466.7</v>
+        <v>3.19</v>
       </c>
       <c r="L4">
-        <v>0.4228887277999275</v>
+        <v>0.1</v>
       </c>
       <c r="M4">
-        <v>154.1</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.04147043784816599</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.3301907006642383</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>139.7</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.03759519900966118</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.2993357617313049</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>14.40000000000001</v>
-      </c>
-      <c r="T4">
-        <v>0.09344581440622976</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1571.9</v>
+        <v>26.3</v>
       </c>
       <c r="V4">
-        <v>0.4230199951559515</v>
+        <v>0.4738738738738739</v>
       </c>
       <c r="W4">
-        <v>0.2055675461392767</v>
+        <v>0.04142857142857143</v>
       </c>
       <c r="X4">
-        <v>0.05881918237561361</v>
+        <v>0.1101649918968362</v>
       </c>
       <c r="Y4">
-        <v>0.1467483637636631</v>
+        <v>-0.06873642046826478</v>
       </c>
       <c r="Z4">
-        <v>1.350646807573216</v>
+        <v>1.107638888888889</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05434779184834464</v>
+        <v>0.08914274469279126</v>
       </c>
       <c r="AC4">
-        <v>-0.05434779184834464</v>
+        <v>-0.08914274469279126</v>
       </c>
       <c r="AD4">
-        <v>874.3</v>
+        <v>43.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>874.3</v>
+        <v>43.5</v>
       </c>
       <c r="AG4">
-        <v>-697.6000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="AH4">
-        <v>0.1904710034421158</v>
+        <v>0.4393939393939394</v>
       </c>
       <c r="AI4">
-        <v>0.2552402639107841</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="AJ4">
-        <v>-0.2311234801046947</v>
+        <v>0.2365887207702888</v>
       </c>
       <c r="AK4">
-        <v>-0.37636903156191</v>
+        <v>0.2202304737516005</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Patria Bank SA (BVB:PBK)</t>
+          <t>Banca Transilvania S.A. (BVB:TLV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -965,6 +959,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.14</v>
+      </c>
+      <c r="E5">
+        <v>0.0688</v>
+      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -978,82 +978,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0.918</v>
+        <v>387.7</v>
       </c>
       <c r="L5">
-        <v>0.02637931034482759</v>
+        <v>0.3805083914024929</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>279.3</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.09195061728395063</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.7204023729687904</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>256.7</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.08451028806584361</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.6621098787722466</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>22.60000000000002</v>
+      </c>
+      <c r="T5">
+        <v>0.08091657715717875</v>
       </c>
       <c r="U5">
-        <v>92.40000000000001</v>
+        <v>1514.1</v>
       </c>
       <c r="V5">
-        <v>1.402124430955994</v>
+        <v>0.4984691358024691</v>
       </c>
       <c r="W5">
-        <v>0.0116497461928934</v>
+        <v>0.1582642772584398</v>
       </c>
       <c r="X5">
-        <v>0.07217099505236713</v>
+        <v>0.1118591060805136</v>
       </c>
       <c r="Y5">
-        <v>-0.06052124885947373</v>
+        <v>0.04640517117792621</v>
       </c>
       <c r="Z5">
-        <v>1.225352112676057</v>
+        <v>0.5832784726793944</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0573865759024344</v>
+        <v>0.08938150522521668</v>
       </c>
       <c r="AC5">
-        <v>-0.0573865759024344</v>
+        <v>-0.08938150522521668</v>
       </c>
       <c r="AD5">
-        <v>44.2</v>
+        <v>2523.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>44.2</v>
+        <v>2523.1</v>
       </c>
       <c r="AG5">
-        <v>-48.2</v>
+        <v>1009</v>
       </c>
       <c r="AH5">
-        <v>0.4014532243415077</v>
+        <v>0.4537459986332409</v>
       </c>
       <c r="AI5">
-        <v>0.3646864686468647</v>
+        <v>0.5447459895934538</v>
       </c>
       <c r="AJ5">
-        <v>-2.723163841807909</v>
+        <v>0.2493512912393426</v>
       </c>
       <c r="AK5">
-        <v>-1.673611111111111</v>
+        <v>0.323646394662561</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/research/traditional_assets/database/data/romania/romania_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.035</v>
+        <v>0.0781</v>
       </c>
       <c r="E2">
-        <v>0.04915</v>
+        <v>0.067125</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0008561360388933237</v>
+        <v>0.0007231539268068054</v>
       </c>
       <c r="J2">
-        <v>0.000738710040502977</v>
+        <v>0.0005977651078403506</v>
       </c>
       <c r="K2">
-        <v>668.89</v>
+        <v>971.34</v>
       </c>
       <c r="L2">
-        <v>0.387245990852776</v>
+        <v>0.4112710644423745</v>
       </c>
       <c r="M2">
-        <v>791.5999999999999</v>
+        <v>15.552</v>
       </c>
       <c r="N2">
-        <v>0.1567555793184023</v>
+        <v>0.002181236763488969</v>
       </c>
       <c r="O2">
-        <v>1.183453183632585</v>
+        <v>0.01601087157946754</v>
       </c>
       <c r="P2">
-        <v>769</v>
+        <v>0.272</v>
       </c>
       <c r="Q2">
-        <v>0.1522802431731322</v>
+        <v>3.814920265361365e-05</v>
       </c>
       <c r="R2">
-        <v>1.149665864342418</v>
+        <v>0.0002800255317396586</v>
       </c>
       <c r="S2">
-        <v>22.60000000000002</v>
+        <v>15.28</v>
       </c>
       <c r="T2">
-        <v>0.02854977261243055</v>
+        <v>0.9825102880658436</v>
       </c>
       <c r="U2">
-        <v>3481.2</v>
+        <v>4588.2</v>
       </c>
       <c r="V2">
-        <v>0.6893601853502049</v>
+        <v>0.6435153368209932</v>
       </c>
       <c r="W2">
-        <v>0.1201798374546083</v>
+        <v>0.2642256708697058</v>
       </c>
       <c r="X2">
-        <v>0.1101649918968362</v>
+        <v>0.08578156667636136</v>
       </c>
       <c r="Y2">
-        <v>0.01001484555777214</v>
+        <v>0.1784441041933444</v>
       </c>
       <c r="Z2">
-        <v>0.6141607234415678</v>
+        <v>0.6098350909861235</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08914274469279126</v>
+        <v>0.07504759700599581</v>
       </c>
       <c r="AC2">
-        <v>-0.08914274469279126</v>
+        <v>-0.0744240029987446</v>
       </c>
       <c r="AD2">
-        <v>4094.5</v>
+        <v>4055.4</v>
       </c>
       <c r="AE2">
-        <v>3.005981100097809</v>
+        <v>4.060275278338437</v>
       </c>
       <c r="AF2">
-        <v>4097.505981100097</v>
+        <v>4059.460275278338</v>
       </c>
       <c r="AG2">
-        <v>616.3059811000976</v>
+        <v>-528.7397247216613</v>
       </c>
       <c r="AH2">
-        <v>0.4479418525389772</v>
+        <v>0.3627964580108543</v>
       </c>
       <c r="AI2">
-        <v>0.5451561587592857</v>
+        <v>0.4705332970631472</v>
       </c>
       <c r="AJ2">
-        <v>0.1087687216376912</v>
+        <v>-0.08009799833247754</v>
       </c>
       <c r="AK2">
-        <v>0.1527397936922187</v>
+        <v>-0.1309033781000992</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>1968.509615384615</v>
+        <v>1609.285714285714</v>
       </c>
       <c r="AP2">
-        <v>296.30095245197</v>
+        <v>-209.8173510800243</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.035</v>
+        <v>0.0261</v>
       </c>
       <c r="E3">
-        <v>0.0295</v>
+        <v>0.00725</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,91 +728,88 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.002185962719852828</v>
+        <v>0.002157040849118859</v>
       </c>
       <c r="J3">
-        <v>0.001800734220531897</v>
+        <v>0.001788209135053962</v>
       </c>
       <c r="K3">
-        <v>278</v>
+        <v>326.9</v>
       </c>
       <c r="L3">
-        <v>0.4109386548410939</v>
+        <v>0.4128567820156605</v>
       </c>
       <c r="M3">
-        <v>512.3</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.2617916091777812</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.842805755395683</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>512.3</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.2617916091777812</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.842805755395683</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>1940.8</v>
+        <v>2010.5</v>
       </c>
       <c r="V3">
-        <v>0.9917727017221114</v>
+        <v>0.7244783971748766</v>
       </c>
       <c r="W3">
-        <v>0.1201798374546083</v>
+        <v>0.2642256708697058</v>
       </c>
       <c r="X3">
-        <v>0.1101117834063283</v>
+        <v>0.08578156667636136</v>
       </c>
       <c r="Y3">
-        <v>0.01006805404828003</v>
+        <v>0.1784441041933444</v>
       </c>
       <c r="Z3">
-        <v>0.652484661867212</v>
+        <v>0.9674617666492332</v>
       </c>
       <c r="AA3">
-        <v>0.001174951458996472</v>
+        <v>0.001730023968937604</v>
       </c>
       <c r="AB3">
-        <v>0.08913504235639216</v>
+        <v>0.07504759700599581</v>
       </c>
       <c r="AC3">
-        <v>-0.08796009089739569</v>
+        <v>-0.0733175730370582</v>
       </c>
       <c r="AD3">
-        <v>1527.9</v>
+        <v>1738.1</v>
       </c>
       <c r="AE3">
-        <v>3.005981100097809</v>
+        <v>4.060275278338437</v>
       </c>
       <c r="AF3">
-        <v>1530.905981100098</v>
+        <v>1742.160275278338</v>
       </c>
       <c r="AG3">
-        <v>-409.894018899902</v>
+        <v>-268.3397247216617</v>
       </c>
       <c r="AH3">
-        <v>0.4389309466741699</v>
+        <v>0.38566745529645</v>
       </c>
       <c r="AI3">
-        <v>0.5506646118916348</v>
+        <v>0.4845309609344471</v>
       </c>
       <c r="AJ3">
-        <v>-0.2649595566582235</v>
+        <v>-0.1070464245696037</v>
       </c>
       <c r="AK3">
-        <v>-0.4883725698733188</v>
+        <v>-0.1692930728924747</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>734.5673076923077</v>
+        <v>689.7222222222222</v>
       </c>
       <c r="AP3">
-        <v>-197.0644321634144</v>
+        <v>-106.4840177466912</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Patria Bank SA (BVB:PBK)</t>
+          <t>Banca Transilvania S.A. (BVB:TLV)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,7 +841,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0004</v>
+        <v>0.122</v>
+      </c>
+      <c r="E4">
+        <v>0.127</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,82 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3.19</v>
+        <v>639.5</v>
       </c>
       <c r="L4">
-        <v>0.1</v>
+        <v>0.4193167661136975</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>12.072</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.002810644688132989</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.01887724784988272</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.272</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>6.332797839398384e-05</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.0004253322908522283</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>11.8</v>
+      </c>
+      <c r="T4">
+        <v>0.9774685222001325</v>
       </c>
       <c r="U4">
-        <v>26.3</v>
+        <v>2553.4</v>
       </c>
       <c r="V4">
-        <v>0.4738738738738739</v>
+        <v>0.5944913971735233</v>
       </c>
       <c r="W4">
-        <v>0.04142857142857143</v>
+        <v>0.3203105434510393</v>
       </c>
       <c r="X4">
-        <v>0.1101649918968362</v>
+        <v>0.0829806361654586</v>
       </c>
       <c r="Y4">
-        <v>-0.06873642046826478</v>
+        <v>0.2373299072855807</v>
       </c>
       <c r="Z4">
-        <v>1.107638888888889</v>
+        <v>0.5117270073482534</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08914274469279126</v>
+        <v>0.0744240029987446</v>
       </c>
       <c r="AC4">
-        <v>-0.08914274469279126</v>
+        <v>-0.0744240029987446</v>
       </c>
       <c r="AD4">
-        <v>43.5</v>
+        <v>2230.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>43.5</v>
+        <v>2230.8</v>
       </c>
       <c r="AG4">
-        <v>17.2</v>
+        <v>-322.5999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.4393939393939394</v>
+        <v>0.3418379074150692</v>
       </c>
       <c r="AI4">
-        <v>0.4166666666666666</v>
+        <v>0.458286254288473</v>
       </c>
       <c r="AJ4">
-        <v>0.2365887207702888</v>
+        <v>-0.08120830711139078</v>
       </c>
       <c r="AK4">
-        <v>0.2202304737516005</v>
+        <v>-0.1393942012703625</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banca Transilvania S.A. (BVB:TLV)</t>
+          <t>Patria Bank SA (BVB:PBK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,10 +963,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.14</v>
-      </c>
-      <c r="E5">
-        <v>0.0688</v>
+        <v>0.0781</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,85 +978,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>387.7</v>
+        <v>4.94</v>
       </c>
       <c r="L5">
-        <v>0.3805083914024929</v>
+        <v>0.1100222717149221</v>
       </c>
       <c r="M5">
-        <v>279.3</v>
+        <v>3.48</v>
       </c>
       <c r="N5">
-        <v>0.09195061728395063</v>
+        <v>0.05829145728643216</v>
       </c>
       <c r="O5">
-        <v>0.7204023729687904</v>
+        <v>0.7044534412955465</v>
       </c>
       <c r="P5">
-        <v>256.7</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.08451028806584361</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.6621098787722466</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>22.60000000000002</v>
+        <v>3.48</v>
       </c>
       <c r="T5">
-        <v>0.08091657715717875</v>
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>1514.1</v>
+        <v>24.3</v>
       </c>
       <c r="V5">
-        <v>0.4984691358024691</v>
+        <v>0.407035175879397</v>
       </c>
       <c r="W5">
-        <v>0.1582642772584398</v>
+        <v>0.08111658456486044</v>
       </c>
       <c r="X5">
-        <v>0.1118591060805136</v>
+        <v>0.1069985079197529</v>
       </c>
       <c r="Y5">
-        <v>0.04640517117792621</v>
+        <v>-0.02588192335489246</v>
       </c>
       <c r="Z5">
-        <v>0.5832784726793944</v>
+        <v>0.6057744198596869</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08938150522521668</v>
+        <v>0.0779783314306759</v>
       </c>
       <c r="AC5">
-        <v>-0.08938150522521668</v>
+        <v>-0.0779783314306759</v>
       </c>
       <c r="AD5">
-        <v>2523.1</v>
+        <v>86.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2523.1</v>
+        <v>86.5</v>
       </c>
       <c r="AG5">
-        <v>1009</v>
+        <v>62.2</v>
       </c>
       <c r="AH5">
-        <v>0.4537459986332409</v>
+        <v>0.5916552667578659</v>
       </c>
       <c r="AI5">
-        <v>0.5447459895934538</v>
+        <v>0.5271176112126752</v>
       </c>
       <c r="AJ5">
-        <v>0.2493512912393426</v>
+        <v>0.5102543068088597</v>
       </c>
       <c r="AK5">
-        <v>0.323646394662561</v>
+        <v>0.4449213161659513</v>
       </c>
       <c r="AL5">
         <v>0</v>
